--- a/content/VTM Paris/VtM Париж.xlsx
+++ b/content/VTM Paris/VtM Париж.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C68BFD8-C416-4474-AA23-E8112B7BECFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533E30EC-9A07-4F56-915A-F155D3CC4A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="314" windowWidth="25370" windowHeight="13759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13759" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="________2025" sheetId="11" r:id="rId1"/>
     <sheet name="черновик" sheetId="12" r:id="rId2"/>
+    <sheet name="октябрь 2025" sheetId="13" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="116">
   <si>
     <t>STR</t>
   </si>
@@ -363,6 +364,12 @@
   </si>
   <si>
     <t>dominance</t>
+  </si>
+  <si>
+    <t>Союзники</t>
+  </si>
+  <si>
+    <t>7 добр, Ч=Созн+Самоконт, Вол=Храбрость</t>
   </si>
 </sst>
 </file>
@@ -465,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,6 +518,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,7 +621,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -687,12 +700,78 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{445E07D5-E06B-4EC2-8A71-367ABD14ECCB}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="0.59996337778862885"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFEB92"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1120,14 +1199,14 @@
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="5" customWidth="1"/>
-    <col min="2" max="5" width="3.109375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="16.109375" style="5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="5" width="3.109375" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="16.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.21875" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.5546875" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="9.21875" style="11" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="9.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.44140625" style="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" style="5"/>
     <col min="15" max="15" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
@@ -1135,8 +1214,8 @@
     <col min="17" max="17" width="6.21875" style="16" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5546875" style="16" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.21875" style="11" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="9.21875" style="11" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="10.21875" style="11" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="9.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13.21875" style="5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.21875" style="5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="5"/>
@@ -2889,40 +2968,40 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:E1048576">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="f">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="f">
       <formula>NOT(ISERROR(SEARCH("f",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="g">
+    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="g">
       <formula>NOT(ISERROR(SEARCH("g",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:L21">
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="22" priority="8">
       <formula>LEN($G14)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="expression" dxfId="13" priority="9">
+    <cfRule type="expression" dxfId="21" priority="9">
       <formula>LEN($P5)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:S4 P5:S5 O25:O32 O34">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="20" priority="7">
       <formula>LEN($P3)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O6:S15 P16:S16 O17:S24">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>LEN($P6)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25:S34">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>LEN($P25)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:AA26">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>$Z19&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4713,36 +4792,1853 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:E1048576">
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="f">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="f">
       <formula>NOT(ISERROR(SEARCH("f",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="g">
+    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="g">
       <formula>NOT(ISERROR(SEARCH("g",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:L21">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>LEN($G14)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="13" priority="9">
       <formula>LEN($P5)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O14:R20 S15:S20 O22:S24">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>LEN($P14)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:S4 P5:S5 O6:S13 O25:O32 O34">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>LEN($P3)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:S21">
+    <cfRule type="expression" dxfId="10" priority="1">
+      <formula>LEN($P21)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P25:S34">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>LEN($P25)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y19:AA26">
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>$Z19&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C51817-A558-468C-A69D-BC9FFED2FF59}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:AF37"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.109375" style="5" customWidth="1"/>
+    <col min="2" max="5" width="3.109375" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="20.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="9.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.88671875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="5"/>
+    <col min="15" max="15" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.21875" style="11" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="9.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" style="5"/>
+    <col min="25" max="25" width="15.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="5" customWidth="1"/>
+    <col min="29" max="29" width="8.88671875" style="5"/>
+    <col min="30" max="30" width="18.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.6640625" style="5" customWidth="1"/>
+    <col min="36" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF1" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="18">
+        <f>SUM(J3:J5)-3</f>
+        <v>3</v>
+      </c>
+      <c r="K2" s="9">
+        <f>SUM(K3:K5)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="9">
+        <f>SUM(L3:L5)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="18">
+        <f>SUM(S3:S12)</f>
+        <v>13</v>
+      </c>
+      <c r="T2" s="9">
+        <f>SUM(T3:T12)</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="9">
+        <f>SUM(U3:U12)</f>
+        <v>2</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA2" s="5">
+        <f>SUM(L2,L6,L10)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF2" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f>REPT("•",SUM(H3:J3))</f>
+        <v>••</v>
+      </c>
+      <c r="I3" s="14"/>
+      <c r="J3" s="16">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="11">
+        <f>5*I3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <f>VLOOKUP(M2,$AD:$AF,2,0)</f>
+        <v>5FB за точку</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <f>REPT("•",SUM(Q3:S3))</f>
+        <v>•••</v>
+      </c>
+      <c r="R3" s="20"/>
+      <c r="S3" s="16">
+        <v>3</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IF(Q3&lt;&gt;1,0,IF(R3+S3=0,3,2*(R3+S3)))</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="11">
+        <f>2*R3</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <f>VLOOKUP(V2,$AD:$AF,2,0)</f>
+        <v>2FB за точку</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>SUM(U2,U13,U24)</f>
+        <v>10</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <f t="shared" ref="G4:G5" si="0">REPT("•",SUM(H4:J4))</f>
+        <v>•••</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="16">
+        <v>3</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11">
+        <f t="shared" ref="L4:L5" si="1">5*I4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="5" t="str">
+        <f t="shared" ref="P4:P12" si="2">REPT("•",SUM(Q4:S4))</f>
+        <v>••</v>
+      </c>
+      <c r="R4" s="20"/>
+      <c r="S4" s="16">
+        <v>2</v>
+      </c>
+      <c r="T4" s="11">
+        <f t="shared" ref="T4:T12" si="3">IF(Q4&lt;&gt;1,0,IF(R4+S4=0,3,2*(R4+S4)))</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="11">
+        <f t="shared" ref="U4:U12" si="4">2*R4</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF4" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>•</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="16">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="O5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="R5" s="20"/>
+      <c r="T5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U5" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA5" s="5">
+        <f>L14</f>
+        <v>7</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE5" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF5" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="18">
+        <f>SUM(J7:J9)-3</f>
+        <v>5</v>
+      </c>
+      <c r="K6" s="9">
+        <f>SUM(K7:K9)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <f>SUM(L7:L9)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>•••</v>
+      </c>
+      <c r="R6" s="20"/>
+      <c r="S6" s="16">
+        <v>3</v>
+      </c>
+      <c r="T6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF6" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="str">
+        <f>REPT("•",SUM(H7:J7))</f>
+        <v>••</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="16">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="11">
+        <f>5*I7</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>••</v>
+      </c>
+      <c r="R7" s="20"/>
+      <c r="S7" s="16">
+        <v>2</v>
+      </c>
+      <c r="T7" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF7" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="5" t="str">
+        <f t="shared" ref="G8:G9" si="5">REPT("•",SUM(H8:J8))</f>
+        <v>•••</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="16">
+        <v>3</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="11">
+        <f t="shared" ref="L8:L9" si="6">5*I8</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>••</v>
+      </c>
+      <c r="R8" s="20">
+        <v>1</v>
+      </c>
+      <c r="S8" s="16">
+        <v>1</v>
+      </c>
+      <c r="T8" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="11">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA8" s="5">
+        <f>L28</f>
+        <v>6</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE8" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>•••</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="16">
+        <v>3</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="R9" s="20"/>
+      <c r="T9" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA9" s="5">
+        <f>SUM(L25:L27)</f>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF9" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="18">
+        <f>SUM(J11:J13)-3</f>
+        <v>7</v>
+      </c>
+      <c r="K10" s="9">
+        <f>SUM(K11:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <f>SUM(L11:L13)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="R10" s="20"/>
+      <c r="T10" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA10" s="5">
+        <f>L23</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF10" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5" t="str">
+        <f>REPT("•",SUM(H11:J11))</f>
+        <v>••••</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="16">
+        <v>4</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="11">
+        <f>5*I11</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="R11" s="20"/>
+      <c r="T11" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>L24</f>
+        <v>3</v>
+      </c>
+      <c r="AD11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF11" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5" t="str">
+        <f t="shared" ref="G12:G13" si="7">REPT("•",SUM(H12:J12))</f>
+        <v>•••</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="16">
+        <v>3</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="11">
+        <f t="shared" ref="L12:L13" si="8">5*I12</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>••</v>
+      </c>
+      <c r="R12" s="20"/>
+      <c r="S12" s="16">
+        <v>2</v>
+      </c>
+      <c r="T12" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>•••</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="16">
+        <v>3</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="18">
+        <f>SUM(S14:S23)</f>
+        <v>5</v>
+      </c>
+      <c r="T13" s="9">
+        <f>SUM(T14:T23)</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <f>SUM(U14:U23)</f>
+        <v>6</v>
+      </c>
+      <c r="Z13" s="6" t="str">
+        <f>(Z15+Z17-Z16)&amp;" fr-b всего"</f>
+        <v>26 fr-b всего</v>
+      </c>
+      <c r="AA13" s="6" t="str">
+        <f>SUM(AA2:AA11)&amp;" потрачено"</f>
+        <v>26 потрачено</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="17">
+        <f>SUM(J15:J21)</f>
+        <v>3</v>
+      </c>
+      <c r="K14" s="12">
+        <f>SUM(K15:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <f>SUM(L15:L21)</f>
+        <v>7</v>
+      </c>
+      <c r="M14" s="35">
+        <v>3</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" s="5" t="str">
+        <f>REPT("•",SUM(Q14:S14))</f>
+        <v>•</v>
+      </c>
+      <c r="R14" s="20"/>
+      <c r="S14" s="16">
+        <v>1</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IF(Q14&lt;&gt;1,0,IF(R14+S14=0,3,2*(R14+S14)))</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <f>2*R14</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="5" t="str">
+        <f t="shared" ref="G15:G21" si="9">REPT("•",SUM(H15:J15))</f>
+        <v>••</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1</v>
+      </c>
+      <c r="J15" s="16">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="11">
+        <f>7*I15</f>
+        <v>7</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="5" t="str">
+        <f t="shared" ref="P15:P23" si="10">REPT("•",SUM(Q15:S15))</f>
+        <v/>
+      </c>
+      <c r="R15" s="20"/>
+      <c r="T15" s="11">
+        <f t="shared" ref="T15:T23" si="11">IF(Q15&lt;&gt;1,0,IF(R15+S15=0,3,2*(R15+S15)))</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="11">
+        <f t="shared" ref="U15:U23" si="12">2*R15</f>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>25</v>
+      </c>
+      <c r="AB15" s="7">
+        <f>(Z15+Z17-Z16)-SUM(AA2:AA11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>•</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="11">
+        <f t="shared" ref="L16:L21" si="13">7*I16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f>VLOOKUP("*"&amp;M15,$AD:$AF,2,0)</f>
+        <v>7FB за точку</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R16" s="20"/>
+      <c r="T16" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z16" s="5">
+        <f>-SUMIF($Z$19:$Z$32,"&lt;0")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>•</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="16">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10"/>
+      <c r="L17" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>••</v>
+      </c>
+      <c r="R17" s="20"/>
+      <c r="S17" s="16">
+        <v>2</v>
+      </c>
+      <c r="T17" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X17"/>
+      <c r="Y17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z17" s="5">
+        <f>SUMIF($Z$19:$Z$32,"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AC17"/>
+    </row>
+    <row r="18" spans="1:29" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="G18" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P18" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R18" s="20"/>
+      <c r="T18" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="G19" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I19" s="14"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" s="5" t="str">
+        <f>REPT("•",SUM(Q19:S19))</f>
+        <v>•</v>
+      </c>
+      <c r="R19" s="20">
+        <v>1</v>
+      </c>
+      <c r="T19" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="11">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="X19"/>
+      <c r="Y19" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z19" s="40">
+        <v>-2</v>
+      </c>
+      <c r="AA19" s="40" t="str">
+        <f>IF(Z19&lt;0,"merit","flaw")</f>
+        <v>merit</v>
+      </c>
+      <c r="AB19"/>
+      <c r="AC19"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="G20" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="5" t="str">
+        <f>REPT("•",SUM(Q20:S20))</f>
+        <v/>
+      </c>
+      <c r="R20" s="20"/>
+      <c r="T20" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X20"/>
+      <c r="Y20" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z20" s="40">
+        <v>-1</v>
+      </c>
+      <c r="AA20" s="40" t="str">
+        <f t="shared" ref="AA20:AA26" si="14">IF(Z20&lt;0,"merit","flaw")</f>
+        <v>merit</v>
+      </c>
+      <c r="AB20"/>
+      <c r="AC20"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="G21" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I21" s="14"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="P21" s="5" t="str">
+        <f t="shared" ref="P21" si="15">REPT("•",SUM(Q21:S21))</f>
+        <v>••</v>
+      </c>
+      <c r="R21" s="20">
+        <v>1</v>
+      </c>
+      <c r="S21" s="16">
+        <v>1</v>
+      </c>
+      <c r="T21" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="11">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="X21"/>
+      <c r="Y21" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z21" s="40">
+        <v>-1</v>
+      </c>
+      <c r="AA21" s="40" t="str">
+        <f>IF(Z21&lt;0,"merit","flaw")</f>
+        <v>merit</v>
+      </c>
+      <c r="AB21"/>
+      <c r="AC21"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="17">
+        <f>SUM(J23:J25)</f>
+        <v>12</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="8">
+        <f>SUM(L23:L25)</f>
+        <v>3</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>••</v>
+      </c>
+      <c r="R22" s="20">
+        <v>1</v>
+      </c>
+      <c r="S22" s="16">
+        <v>1</v>
+      </c>
+      <c r="T22" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="11">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="X22"/>
+      <c r="Y22" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z22" s="40">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="40" t="str">
+        <f>IF(Z22&lt;0,"merit","flaw")</f>
+        <v>flaw</v>
+      </c>
+      <c r="AB22"/>
+      <c r="AC22"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="39" t="str">
+        <f>IF(SUM(H23:K23)&gt;=5,"⑤ "&amp;REPT("•",SUM(H23:K23)-5),REPT("•",SUM(H23:K23)))</f>
+        <v>⑤ •</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="38">
+        <f>J25+J26</f>
+        <v>6</v>
+      </c>
+      <c r="K23" s="10"/>
+      <c r="L23" s="11">
+        <f>1*I23</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f>VLOOKUP(F23,$AD:$AF,2,0)</f>
+        <v>1FB за точку</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R23" s="20"/>
+      <c r="T23" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X23"/>
+      <c r="Y23" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z23" s="40">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="40" t="str">
+        <f>IF(Z23&lt;0,"merit","flaw")</f>
+        <v>flaw</v>
+      </c>
+      <c r="AB23"/>
+      <c r="AC23"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="39" t="str">
+        <f>IF(SUM(H24:K24)&gt;=5,"⑤ "&amp;REPT("•",SUM(H24:K24)-5),REPT("•",SUM(H24:K24)))</f>
+        <v>⑤ ••</v>
+      </c>
+      <c r="I24" s="14">
+        <v>3</v>
+      </c>
+      <c r="J24" s="38">
+        <f>J27</f>
+        <v>4</v>
+      </c>
+      <c r="L24" s="11">
+        <f>1*I24</f>
+        <v>3</v>
+      </c>
+      <c r="M24" s="5" t="str">
+        <f>VLOOKUP(F24,$AD:$AF,2,0)</f>
+        <v>1FB за точку</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="18">
+        <f>SUM(S25:S34)</f>
+        <v>9</v>
+      </c>
+      <c r="T24" s="9">
+        <f>SUM(T25:T34)</f>
+        <v>3</v>
+      </c>
+      <c r="U24" s="9">
+        <f>SUM(U25:U34)</f>
+        <v>2</v>
+      </c>
+      <c r="X24"/>
+      <c r="Y24" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z24" s="40">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="40" t="str">
+        <f>IF(Z24&lt;0,"merit","flaw")</f>
+        <v>flaw</v>
+      </c>
+      <c r="AB24"/>
+      <c r="AC24"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F25" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="5" t="str">
+        <f t="shared" ref="G25:G27" si="16">REPT("•",SUM(H25:J25))</f>
+        <v>••</v>
+      </c>
+      <c r="H25" s="36"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="36">
+        <v>2</v>
+      </c>
+      <c r="K25" s="36"/>
+      <c r="L25" s="11">
+        <f>2*I25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="37" t="str">
+        <f>VLOOKUP("Добродетель",$AD:$AF,2,0)</f>
+        <v>2FB за точку</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P25" s="5" t="str">
+        <f>REPT("•",SUM(Q25:S25))</f>
+        <v>•</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>1</v>
+      </c>
+      <c r="R25" s="20"/>
+      <c r="T25" s="11">
+        <f>IF(Q25&lt;&gt;1,0,IF(R25+S25=0,3,2*(R25+S25)))</f>
+        <v>3</v>
+      </c>
+      <c r="U25" s="11">
+        <f>2*R25</f>
+        <v>0</v>
+      </c>
+      <c r="X25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F26" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>••••</v>
+      </c>
+      <c r="H26" s="36"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="36">
+        <v>4</v>
+      </c>
+      <c r="K26" s="36"/>
+      <c r="L26" s="11">
+        <f t="shared" ref="L26:L27" si="17">2*I26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="37" t="str">
+        <f t="shared" ref="M26:M27" si="18">VLOOKUP("Добродетель",$AD:$AF,2,0)</f>
+        <v>2FB за точку</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P26" s="5" t="str">
+        <f t="shared" ref="P26:P34" si="19">REPT("•",SUM(Q26:S26))</f>
+        <v>•</v>
+      </c>
+      <c r="R26" s="20"/>
+      <c r="S26" s="16">
+        <v>1</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" ref="T26:T34" si="20">IF(Q26&lt;&gt;1,0,IF(R26+S26=0,3,2*(R26+S26)))</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="11">
+        <f t="shared" ref="U26:U34" si="21">2*R26</f>
+        <v>0</v>
+      </c>
+      <c r="X26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F27" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>••••</v>
+      </c>
+      <c r="H27" s="36"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="36">
+        <v>4</v>
+      </c>
+      <c r="K27" s="36"/>
+      <c r="L27" s="11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>2FB за точку</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P27" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="R27" s="20"/>
+      <c r="T27" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="17">
+        <f>SUM(J29:J37)</f>
+        <v>5</v>
+      </c>
+      <c r="K28" s="8">
+        <f>SUM(K29:K37)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <f>SUM(L29:L37)</f>
+        <v>6</v>
+      </c>
+      <c r="M28" s="5">
+        <v>5</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>•</v>
+      </c>
+      <c r="R28" s="20"/>
+      <c r="S28" s="16">
+        <v>1</v>
+      </c>
+      <c r="T28" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="5" t="str">
+        <f>REPT("•",SUM(H29:J29))</f>
+        <v>••••</v>
+      </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="16">
+        <v>4</v>
+      </c>
+      <c r="K29" s="10"/>
+      <c r="L29" s="11">
+        <f>I29</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="R29" s="20"/>
+      <c r="T29" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="5" t="str">
+        <f>REPT("•",SUM(H30:J30))</f>
+        <v>•</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="16">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="11">
+        <f>I30</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="str">
+        <f>VLOOKUP(M29,$AD:$AF,2,0)</f>
+        <v>1FB за точку</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P30" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>••</v>
+      </c>
+      <c r="R30" s="20"/>
+      <c r="S30" s="16">
+        <v>2</v>
+      </c>
+      <c r="T30" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="5">
+        <f>POWER(2,SUM(Q30:S30,-1))</f>
+        <v>2</v>
+      </c>
+      <c r="W30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F31" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f>REPT("•",SUM(H31:J31))</f>
+        <v>•</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10"/>
+      <c r="L31" s="11">
+        <f>I31</f>
+        <v>1</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P31" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>••</v>
+      </c>
+      <c r="R31" s="20"/>
+      <c r="S31" s="16">
+        <v>2</v>
+      </c>
+      <c r="T31" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="F32" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="5" t="str">
+        <f>REPT("•",SUM(H32:J32))</f>
+        <v>•••</v>
+      </c>
+      <c r="H32" s="16">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14">
+        <v>1</v>
+      </c>
+      <c r="K32" s="10"/>
+      <c r="L32" s="11">
+        <f>I32</f>
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>•••</v>
+      </c>
+      <c r="R32" s="20">
+        <v>1</v>
+      </c>
+      <c r="S32" s="16">
+        <v>2</v>
+      </c>
+      <c r="T32" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="11">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="6:21" x14ac:dyDescent="0.3">
+      <c r="F33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="5" t="str">
+        <f>REPT("•",SUM(H33:J33))</f>
+        <v>•</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="10"/>
+      <c r="L33" s="11">
+        <f>I33</f>
+        <v>1</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P33" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="R33" s="20"/>
+      <c r="T33" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="6:21" x14ac:dyDescent="0.3">
+      <c r="F34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f t="shared" ref="G34:G35" si="22">REPT("•",SUM(H34:J34))</f>
+        <v>••</v>
+      </c>
+      <c r="I34" s="14">
+        <v>2</v>
+      </c>
+      <c r="K34" s="10"/>
+      <c r="L34" s="11">
+        <f t="shared" ref="L34:L35" si="23">I34</f>
+        <v>2</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>•</v>
+      </c>
+      <c r="R34" s="20"/>
+      <c r="S34" s="16">
+        <v>1</v>
+      </c>
+      <c r="T34" s="11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="6:21" x14ac:dyDescent="0.3">
+      <c r="F35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="5" t="str">
+        <f t="shared" si="22"/>
+        <v>•</v>
+      </c>
+      <c r="I35" s="14">
+        <v>1</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="11">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="6:21" x14ac:dyDescent="0.3">
+      <c r="K36" s="10"/>
+    </row>
+    <row r="37" spans="6:21" x14ac:dyDescent="0.3">
+      <c r="K37" s="10"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:E1048576">
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="f">
+      <formula>NOT(ISERROR(SEARCH("f",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="g">
+      <formula>NOT(ISERROR(SEARCH("g",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:L21">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>LEN($G14)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N6">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>LEN($P5)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:S4 P5:S5 O25:O32 O34">
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>LEN($P3)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O6:S15 P16:S16 O17:S24">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>LEN($P21)&gt;0</formula>
+      <formula>LEN($P6)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25:S34">
@@ -4750,7 +6646,7 @@
       <formula>LEN($P25)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y19:AA26">
+  <conditionalFormatting sqref="Y19:AA24">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>$Z19&lt;0</formula>
     </cfRule>
